--- a/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
+++ b/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="59">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modele metier FRLMParticipantCorps vers le profil CDA FRCDAParticipant, puis vers l'extension FHIR FRActorExtension.</t>
+    <t>Mapping des éléments du modèle métier FRLMParticipant vers le profil CDA FRCDAParticipant, puis vers l'extension FHIR FRActorExtension.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant</t>
   </si>
   <si>
     <t/>
@@ -109,7 +109,7 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-participant</t>
   </si>
   <si>
-    <t>FRLMParticipantCorps</t>
+    <t>FRLMParticipant</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -118,102 +118,54 @@
     <t>FRCDAParticipant</t>
   </si>
   <si>
-    <t>FRLMParticipantCorps.dateEtHeureParticipation</t>
+    <t>FRLMParticipant.identifier</t>
+  </si>
+  <si>
+    <t>FRCDAParticipant.participantRole.id</t>
+  </si>
+  <si>
+    <t>FRLMParticipant.name</t>
+  </si>
+  <si>
+    <t>FRCDAParticipant.participantRole.playingEntity.name</t>
+  </si>
+  <si>
+    <t>FRLMParticipant.type</t>
+  </si>
+  <si>
+    <t>FRCDAParticipant.code</t>
+  </si>
+  <si>
+    <t>FRLMParticipant.role</t>
+  </si>
+  <si>
+    <t>FRCDAParticipant.participantRole.playingEntity.code</t>
+  </si>
+  <si>
+    <t>FRLMParticipant.period</t>
   </si>
   <si>
     <t>FRCDAParticipant.time</t>
   </si>
   <si>
-    <t>FRLMParticipantCorps.participantRole.IdentifiantParticipant</t>
-  </si>
-  <si>
-    <t>FRCDAParticipant.participantRole.id</t>
-  </si>
-  <si>
-    <t>FRLMParticipantCorps.participantRole.typeParticipant</t>
-  </si>
-  <si>
-    <t>FRCDAParticipant.code</t>
-  </si>
-  <si>
-    <t>FRLMParticipantCorps.participantRole.adresses</t>
-  </si>
-  <si>
-    <t>FRCDAParticipant.participantRole.addr</t>
-  </si>
-  <si>
-    <t>FRLMParticipantCorps.participantRole.coordonneesTelecom</t>
-  </si>
-  <si>
-    <t>FRCDAParticipant.participantRole.telecom</t>
-  </si>
-  <si>
-    <t>FRLMParticipantCorps.participantRole.identiteParticipant.nom</t>
-  </si>
-  <si>
-    <t>FRCDAParticipant.participantRole.playingEntity.name</t>
-  </si>
-  <si>
-    <t>FRLMParticipantCorps.participantRole.identiteParticipant.ProfessionSpecialite</t>
-  </si>
-  <si>
-    <t>FRCDAParticipant.participantRole.playingEntity.code</t>
-  </si>
-  <si>
-    <t>FRLMParticipantCorps.participantRole.identiteParticipant.description</t>
-  </si>
-  <si>
-    <t>FRCDAParticipant.participantRole.playingEntity.desc</t>
-  </si>
-  <si>
-    <t>FRLMParticipantCorps.participantRole.Organisation</t>
+    <t>FRLMParticipant.participant.participantProfessional</t>
+  </si>
+  <si>
+    <t>FRCDAParticipant.participantRole.playingEntity</t>
+  </si>
+  <si>
+    <t>FRLMParticipant.participant.participantDevice</t>
+  </si>
+  <si>
+    <t>FRCDAParticipant.participantRole.playingDevice</t>
+  </si>
+  <si>
+    <t>FRLMParticipant.participant.participantOrganisation</t>
   </si>
   <si>
     <t>FRCDAParticipant.participantRole.scopingEntity</t>
   </si>
   <si>
-    <t>FRLMParticipantCorps.participantRole.Organisation.identifiant</t>
-  </si>
-  <si>
-    <t>FRCDAParticipant.participantRole.scopingEntity.id</t>
-  </si>
-  <si>
-    <t>FRLMParticipantCorps.participantRole.Organisation.code</t>
-  </si>
-  <si>
-    <t>FRCDAParticipant.participantRole.scopingEntity.code</t>
-  </si>
-  <si>
-    <t>FRLMParticipantCorps.participantRole.Organisation.description</t>
-  </si>
-  <si>
-    <t>FRCDAParticipant.participantRole.scopingEntity.desc</t>
-  </si>
-  <si>
-    <t>FRLMParticipantCorps.participantRole.dispositifAutomatique</t>
-  </si>
-  <si>
-    <t>FRCDAParticipant.participantRole.playingDevice</t>
-  </si>
-  <si>
-    <t>FRLMParticipantCorps.participantRole.categorie</t>
-  </si>
-  <si>
-    <t>FRCDAParticipant.participantRole.playingDevice.code</t>
-  </si>
-  <si>
-    <t>FRLMParticipantCorps.participantRole.nomModele</t>
-  </si>
-  <si>
-    <t>FRCDAParticipant.participantRole.playingDevice.manufacturerModelName</t>
-  </si>
-  <si>
-    <t>FRLMParticipantCorps.participantRole.nomLogiciel</t>
-  </si>
-  <si>
-    <t>FRCDAParticipant.participantRole.playingDevice.softwareName</t>
-  </si>
-  <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
   </si>
   <si>
@@ -226,40 +178,19 @@
     <t>FRActorExtension.extension[actor].value[x]:FRPractitionerRoleDocument.identifier</t>
   </si>
   <si>
-    <t>FRActorExtension.extension[actor].value[x]:FRPractitionerRoleDocument.address</t>
-  </si>
-  <si>
-    <t>FRActorExtension.extension[actor].value[x]:FRPractitionerRoleDocument.telecom</t>
-  </si>
-  <si>
     <t>FRActorExtension.extension[actor].value[x]:FRPractitionerRoleDocument.name</t>
   </si>
   <si>
     <t>FRActorExtension.extension[actor].value[x]:FRPractitionerRoleDocument.practitioner.qualification</t>
   </si>
   <si>
-    <t>FRActorExtension.extension[actor].value[x]:FROrganizationDocument</t>
-  </si>
-  <si>
-    <t>FRActorExtension.extension[actor].value[x]:FROrganizationDocument.identifier</t>
-  </si>
-  <si>
-    <t>FRActorExtension.extension[actor].value[x]:FROrganizationDocument.type</t>
-  </si>
-  <si>
-    <t>FRActorExtension.extension[actor].value[x]:FROrganizationDocument.extension:description</t>
+    <t>FRActorExtension.extension[actor].value[x]:FRPractitionerRoleDocument</t>
   </si>
   <si>
     <t>FRActorExtension.extension[actor].value[x]:Device</t>
   </si>
   <si>
-    <t>FRActorExtension.extension[actor].value[x]:Device.type</t>
-  </si>
-  <si>
-    <t>FRActorExtension.extension[actor].value[x]:Device.manufacturer</t>
-  </si>
-  <si>
-    <t>FRActorExtension.extension[actor].value[x]:Device.deviceName.name</t>
+    <t>FRActorExtension.extension[actor].value[x]:FROrganizationRoleDocument</t>
   </si>
 </sst>
 </file>
@@ -511,7 +442,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -664,110 +595,6 @@
         <v>49</v>
       </c>
       <c r="E11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D19" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="E19" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -776,7 +603,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -798,7 +625,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -807,7 +634,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -815,198 +642,107 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E17" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
+++ b/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
+++ b/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
+++ b/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
+++ b/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
+++ b/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
+++ b/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
+++ b/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-participant|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-participant</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-participant</t>
   </si>
   <si>
     <t>FRLMParticipant</t>
@@ -166,7 +166,7 @@
     <t>FRCDAParticipant.participantRole.scopingEntity</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension|0.1.0</t>
   </si>
   <si>
     <t>FRActorExtension</t>

--- a/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
+++ b/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
@@ -9,12 +9,13 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Mapping Table 0" r:id="rId4" sheetId="2"/>
     <sheet name="Mapping Table 1" r:id="rId5" sheetId="3"/>
+    <sheet name="Mapping Table 2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="59">
   <si>
     <t>Property</t>
   </si>
@@ -37,6 +38,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>FRParticipantCorpsLMCDAFHIR</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -52,10 +56,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:45:34+00:00</t>
+    <t>2026-08-31T15:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +107,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-participant|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMParticipant|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-participant</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-participant-corps|0.1.0</t>
   </si>
   <si>
     <t>FRLMParticipant</t>
@@ -115,82 +122,76 @@
     <t>equivalent</t>
   </si>
   <si>
+    <t>Participant2</t>
+  </si>
+  <si>
     <t>FRCDAParticipant</t>
   </si>
   <si>
+    <t>FRLMParticipant.type</t>
+  </si>
+  <si>
+    <t>Participant2.typeCode</t>
+  </si>
+  <si>
+    <t>FRLMParticipant.period</t>
+  </si>
+  <si>
+    <t>Participant2.time</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-participant-role|0.1.0</t>
+  </si>
+  <si>
     <t>FRLMParticipant.identifier</t>
   </si>
   <si>
-    <t>FRCDAParticipant.participantRole.id</t>
+    <t>ParticipantRole.id</t>
   </si>
   <si>
     <t>FRLMParticipant.name</t>
   </si>
   <si>
-    <t>FRCDAParticipant.participantRole.playingEntity.name</t>
-  </si>
-  <si>
-    <t>FRLMParticipant.type</t>
-  </si>
-  <si>
-    <t>FRCDAParticipant.code</t>
+    <t>source-is-narrower-than-target</t>
+  </si>
+  <si>
+    <t>ParticipantRole.playingEntity</t>
   </si>
   <si>
     <t>FRLMParticipant.role</t>
   </si>
   <si>
-    <t>FRCDAParticipant.participantRole.playingEntity.code</t>
-  </si>
-  <si>
-    <t>FRLMParticipant.period</t>
-  </si>
-  <si>
-    <t>FRCDAParticipant.time</t>
+    <t>ParticipantRole.code</t>
   </si>
   <si>
     <t>FRLMParticipant.participant.participantProfessional</t>
   </si>
   <si>
-    <t>FRCDAParticipant.participantRole.playingEntity</t>
-  </si>
-  <si>
     <t>FRLMParticipant.participant.participantDevice</t>
   </si>
   <si>
-    <t>FRCDAParticipant.participantRole.playingDevice</t>
+    <t>ParticipantRole.playingDevice</t>
   </si>
   <si>
     <t>FRLMParticipant.participant.participantOrganisation</t>
   </si>
   <si>
-    <t>FRCDAParticipant.participantRole.scopingEntity</t>
+    <t>ParticipantRole.scopingEntity</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension|0.1.0</t>
   </si>
   <si>
+    <t>Extension</t>
+  </si>
+  <si>
     <t>FRActorExtension</t>
   </si>
   <si>
-    <t>FRActorExtension.extension[typeCode].value[x]</t>
-  </si>
-  <si>
-    <t>FRActorExtension.extension[actor].value[x]:FRPractitionerRoleDocument.identifier</t>
-  </si>
-  <si>
-    <t>FRActorExtension.extension[actor].value[x]:FRPractitionerRoleDocument.name</t>
-  </si>
-  <si>
-    <t>FRActorExtension.extension[actor].value[x]:FRPractitionerRoleDocument.practitioner.qualification</t>
-  </si>
-  <si>
-    <t>FRActorExtension.extension[actor].value[x]:FRPractitionerRoleDocument</t>
-  </si>
-  <si>
-    <t>FRActorExtension.extension[actor].value[x]:Device</t>
-  </si>
-  <si>
-    <t>FRActorExtension.extension[actor].value[x]:FROrganizationRoleDocument</t>
+    <t>Extension.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension:actor.value[x]</t>
   </si>
 </sst>
 </file>
@@ -359,79 +360,83 @@
       <c r="A4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" t="s" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
@@ -442,159 +447,83 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="E11" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -603,141 +532,265 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>58</v>

--- a/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
+++ b/main/ig/FRParticipantCorpsLMCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
